--- a/Work_Track.xlsx
+++ b/Work_Track.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\Dinesh_Academic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dinesh_Academic\Projects\VS_Projects\ProfApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80569239-3E90-4E32-8603-B2BFE194293D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A8FE3F-5096-4670-8B70-A3ECEDF42D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="602" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="602" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Academic" sheetId="2" r:id="rId1"/>
-    <sheet name="Admin-Addl." sheetId="8" r:id="rId2"/>
-    <sheet name="PhD Supervision" sheetId="11" r:id="rId3"/>
-    <sheet name="Pipeline" sheetId="1" r:id="rId4"/>
-    <sheet name="Published" sheetId="3" r:id="rId5"/>
-    <sheet name="Book Chapter" sheetId="7" r:id="rId6"/>
-    <sheet name="Projects" sheetId="9" r:id="rId7"/>
-    <sheet name="Conferences" sheetId="4" r:id="rId8"/>
-    <sheet name="Ideas" sheetId="5" r:id="rId9"/>
-    <sheet name="History_record" sheetId="6" r:id="rId10"/>
+    <sheet name="Work Exp" sheetId="12" r:id="rId2"/>
+    <sheet name="Admin-Addl." sheetId="8" r:id="rId3"/>
+    <sheet name="PhD Supervision" sheetId="11" r:id="rId4"/>
+    <sheet name="Pipeline" sheetId="1" r:id="rId5"/>
+    <sheet name="Published" sheetId="3" r:id="rId6"/>
+    <sheet name="Book Chapter" sheetId="7" r:id="rId7"/>
+    <sheet name="Projects" sheetId="9" r:id="rId8"/>
+    <sheet name="Conferences" sheetId="4" r:id="rId9"/>
+    <sheet name="Ideas" sheetId="5" r:id="rId10"/>
+    <sheet name="History_record" sheetId="6" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="285">
   <si>
     <t>S. No.</t>
   </si>
@@ -886,6 +887,9 @@
   </si>
   <si>
     <t>Digital Technologies and Women Entrepreneurship in Morocco: Strategic Factors and Their Impacts</t>
+  </si>
+  <si>
+    <t>Work Exp</t>
   </si>
 </sst>
 </file>
@@ -1157,17 +1161,32 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1177,21 +1196,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1587,24 +1591,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8EC06E-E612-4927-AA85-EB849A64B331}">
   <dimension ref="B4:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="34"/>
-    <col min="2" max="2" width="6.5703125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="34" customWidth="1"/>
-    <col min="4" max="4" width="37.7109375" style="34" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="34"/>
+    <col min="2" max="2" width="6.54296875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="37.7265625" style="34" customWidth="1"/>
+    <col min="5" max="6" width="14.54296875" style="4" customWidth="1"/>
     <col min="7" max="7" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="34"/>
+    <col min="8" max="16384" width="8.7265625" style="34"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C4" s="33" t="s">
         <v>169</v>
       </c>
       <c r="D4" s="33"/>
     </row>
-    <row r="5" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1624,7 +1628,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="14">
         <v>1</v>
       </c>
@@ -1642,7 +1646,7 @@
         <v>83.6</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="14">
         <v>2</v>
       </c>
@@ -1660,7 +1664,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="31" x14ac:dyDescent="0.35">
       <c r="B8" s="14">
         <v>3</v>
       </c>
@@ -1680,7 +1684,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="14">
         <v>4</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="14">
         <v>5</v>
       </c>
@@ -1720,18 +1724,18 @@
         <v>9.4779999999999998</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="35"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C12" s="33" t="s">
         <v>170</v>
       </c>
       <c r="D12" s="33"/>
     </row>
-    <row r="13" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1751,7 +1755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="14">
         <v>1</v>
       </c>
@@ -1771,7 +1775,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="14">
         <v>2</v>
       </c>
@@ -1791,7 +1795,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="14">
         <v>3</v>
       </c>
@@ -1811,7 +1815,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="14">
         <v>4</v>
       </c>
@@ -1831,7 +1835,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="14">
         <v>5</v>
       </c>
@@ -1851,7 +1855,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="14">
         <v>6</v>
       </c>
@@ -1877,24 +1881,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBA2258-CB44-44B4-BF65-F9693BF7E65D}">
-  <dimension ref="A2:J45"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329D78CB-96B5-4BE9-A9C4-C501614BBAAD}">
+  <dimension ref="A2:J44"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="6"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="22.7265625" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1926,143 +1930,99 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="17">
-        <v>45056</v>
-      </c>
-      <c r="I3" s="17">
-        <v>45056</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15"/>
+        <v>119</v>
+      </c>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="17">
-        <v>45125</v>
-      </c>
-      <c r="I4" s="17">
-        <v>45215</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="15"/>
+        <v>120</v>
+      </c>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="17">
-        <v>45268</v>
-      </c>
-      <c r="I5" s="17">
-        <v>45278</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="17">
-        <v>45685</v>
-      </c>
-      <c r="I6" s="17">
-        <v>45640</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="15"/>
+    </row>
+    <row r="7" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="16"/>
       <c r="C7" s="15"/>
       <c r="D7" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="15">
-        <v>250202600</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="17">
-        <v>45685</v>
-      </c>
-      <c r="I7" s="17">
-        <v>45687</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="16"/>
       <c r="C8" s="15"/>
@@ -2074,39 +2034,19 @@
       <c r="I8" s="17"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
-        <v>2</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H9" s="17">
-        <v>45737</v>
-      </c>
-      <c r="I9" s="17">
-        <v>45747</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="14"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="15"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10" s="15"/>
@@ -2118,37 +2058,19 @@
       <c r="I10" s="17"/>
       <c r="J10" s="15"/>
     </row>
-    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
-        <v>3</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>17</v>
-      </c>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="14"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="15"/>
-      <c r="G11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="17">
-        <v>45684</v>
-      </c>
-      <c r="I11" s="17">
-        <v>45685</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -2160,7 +2082,7 @@
       <c r="I12" s="14"/>
       <c r="J12" s="15"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13" s="15"/>
@@ -2172,7 +2094,7 @@
       <c r="I13" s="14"/>
       <c r="J13" s="15"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -2184,7 +2106,7 @@
       <c r="I14" s="14"/>
       <c r="J14" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -2196,7 +2118,7 @@
       <c r="I15" s="14"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="15"/>
@@ -2208,7 +2130,7 @@
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -2220,7 +2142,7 @@
       <c r="I17" s="14"/>
       <c r="J17" s="15"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -2232,7 +2154,7 @@
       <c r="I18" s="14"/>
       <c r="J18" s="15"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -2244,7 +2166,7 @@
       <c r="I19" s="14"/>
       <c r="J19" s="15"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -2256,7 +2178,7 @@
       <c r="I20" s="14"/>
       <c r="J20" s="15"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -2268,7 +2190,7 @@
       <c r="I21" s="14"/>
       <c r="J21" s="15"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -2280,7 +2202,7 @@
       <c r="I22" s="14"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -2292,7 +2214,7 @@
       <c r="I23" s="14"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -2304,7 +2226,7 @@
       <c r="I24" s="14"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -2316,7 +2238,7 @@
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -2328,7 +2250,692 @@
       <c r="I26" s="14"/>
       <c r="J26" s="15"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="22"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="22"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="21"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="21"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="21"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="21"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="21"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="21"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="21"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J3:J36">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"Accept"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"Under Review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Reject"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBA2258-CB44-44B4-BF65-F9693BF7E65D}">
+  <dimension ref="A2:J45"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="24" style="13" customWidth="1"/>
+    <col min="4" max="4" width="50" style="8" customWidth="1"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="22.7265625" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="17">
+        <v>45056</v>
+      </c>
+      <c r="I3" s="17">
+        <v>45056</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="17">
+        <v>45125</v>
+      </c>
+      <c r="I4" s="17">
+        <v>45215</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="14"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="17">
+        <v>45268</v>
+      </c>
+      <c r="I5" s="17">
+        <v>45278</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="17">
+        <v>45685</v>
+      </c>
+      <c r="I6" s="17">
+        <v>45640</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A7" s="14"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="15">
+        <v>250202600</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="17">
+        <v>45685</v>
+      </c>
+      <c r="I7" s="17">
+        <v>45687</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="14"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>2</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H9" s="17">
+        <v>45737</v>
+      </c>
+      <c r="I9" s="17">
+        <v>45747</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="14"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="14">
+        <v>3</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="17">
+        <v>45684</v>
+      </c>
+      <c r="I11" s="17">
+        <v>45685</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="14"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="14"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="14"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="14"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="14"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="14"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="15"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="14"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="15"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="14"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="14"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="15"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="14"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="14"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="15"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
@@ -2340,7 +2947,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
       <c r="B28" s="23"/>
       <c r="C28" s="22"/>
@@ -2352,7 +2959,7 @@
       <c r="I28" s="21"/>
       <c r="J28" s="22"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="23"/>
       <c r="C29" s="22"/>
@@ -2364,7 +2971,7 @@
       <c r="I29" s="21"/>
       <c r="J29" s="22"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
       <c r="B30" s="23"/>
       <c r="C30" s="22"/>
@@ -2376,7 +2983,7 @@
       <c r="I30" s="21"/>
       <c r="J30" s="21"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="23"/>
       <c r="C31" s="22"/>
@@ -2388,7 +2995,7 @@
       <c r="I31" s="21"/>
       <c r="J31" s="21"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
       <c r="B32" s="23"/>
       <c r="C32" s="22"/>
@@ -2400,7 +3007,7 @@
       <c r="I32" s="21"/>
       <c r="J32" s="21"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="23"/>
       <c r="C33" s="22"/>
@@ -2412,7 +3019,7 @@
       <c r="I33" s="21"/>
       <c r="J33" s="21"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="23"/>
       <c r="C34" s="22"/>
@@ -2424,7 +3031,7 @@
       <c r="I34" s="21"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="23"/>
       <c r="C35" s="22"/>
@@ -2436,7 +3043,7 @@
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
       <c r="B36" s="23"/>
       <c r="C36" s="22"/>
@@ -2448,7 +3055,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="23"/>
       <c r="C37" s="22"/>
@@ -2460,7 +3067,7 @@
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="26"/>
       <c r="C38" s="12"/>
@@ -2472,7 +3079,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="26"/>
       <c r="C39" s="12"/>
@@ -2484,7 +3091,7 @@
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="26"/>
       <c r="C40" s="12"/>
@@ -2496,7 +3103,7 @@
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -2508,7 +3115,7 @@
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -2520,7 +3127,7 @@
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -2532,7 +3139,7 @@
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -2544,7 +3151,7 @@
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="9"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -2574,113 +3181,164 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22B272B-95DC-48E8-A0D6-8CBC0A7F26A7}">
-  <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0D01FD-168F-4E05-9976-928259C73ACA}">
+  <dimension ref="B4:G11"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="50.5703125" style="34" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="4" customWidth="1"/>
-    <col min="4" max="5" width="10.5703125" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="8.7265625" style="34"/>
+    <col min="2" max="2" width="6.54296875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" style="34" customWidth="1"/>
+    <col min="4" max="4" width="37.7265625" style="34" customWidth="1"/>
+    <col min="5" max="6" width="14.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="34"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C4" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="33"/>
+    </row>
+    <row r="5" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="C5" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="17">
-        <v>45883</v>
-      </c>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="C6" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="38">
+        <v>44216</v>
+      </c>
+      <c r="F6" s="38">
+        <v>44742</v>
+      </c>
+      <c r="G6" s="46">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="17">
-        <v>45883</v>
-      </c>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="C7" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="38">
+        <v>44743</v>
+      </c>
+      <c r="F7" s="38">
+        <v>44926</v>
+      </c>
+      <c r="G7" s="46">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="17">
-        <v>45883</v>
-      </c>
-      <c r="E6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="C8" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="38">
+        <v>45057</v>
+      </c>
+      <c r="F8" s="38">
+        <v>45169</v>
+      </c>
+      <c r="G8" s="46">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D7" s="17">
-        <v>45883</v>
-      </c>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="C9" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="38">
+        <v>45200</v>
+      </c>
+      <c r="F9" s="38">
+        <v>45291</v>
+      </c>
+      <c r="G9" s="46">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="14">
         <v>5</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="11" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
+      <c r="C10" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="38">
+        <v>45306</v>
+      </c>
+      <c r="F10" s="38">
+        <v>45869</v>
+      </c>
+      <c r="G10" s="46">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="14">
+        <v>6</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="38">
+        <v>45880</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" s="14">
+        <v>111188</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2688,24 +3346,138 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D22B272B-95DC-48E8-A0D6-8CBC0A7F26A7}">
+  <dimension ref="A2:E11"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.54296875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50.54296875" style="34" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="10.54296875" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="34"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>1</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="17">
+        <v>45883</v>
+      </c>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>2</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="17">
+        <v>45883</v>
+      </c>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>3</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="17">
+        <v>45883</v>
+      </c>
+      <c r="E6" s="14"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="14">
+        <v>4</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="17">
+        <v>45883</v>
+      </c>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
+        <v>5</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row r="11" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC687A47-0B0C-40A2-9930-B5946927E077}">
   <dimension ref="A3:L72"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" style="44" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" style="44" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" style="44" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="44" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="44" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="44" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="44" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="44" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" style="44" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="44"/>
+    <col min="1" max="1" width="5.54296875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" style="44" customWidth="1"/>
+    <col min="3" max="4" width="16.7265625" style="44" customWidth="1"/>
+    <col min="5" max="5" width="30.7265625" style="44" customWidth="1"/>
+    <col min="6" max="6" width="16.7265625" style="44" customWidth="1"/>
+    <col min="7" max="7" width="20.7265625" style="44" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" style="44" customWidth="1"/>
+    <col min="9" max="9" width="18.7265625" style="44" customWidth="1"/>
+    <col min="10" max="11" width="14.7265625" style="44" customWidth="1"/>
+    <col min="12" max="12" width="20.7265625" style="44" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="44"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2743,7 +3515,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>1</v>
       </c>
@@ -2765,7 +3537,7 @@
       <c r="K4" s="45"/>
       <c r="L4" s="45"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>2</v>
       </c>
@@ -2789,7 +3561,7 @@
       <c r="K5" s="45"/>
       <c r="L5" s="45"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="14"/>
       <c r="B6" s="45"/>
       <c r="C6" s="45"/>
@@ -2803,7 +3575,7 @@
       <c r="K6" s="45"/>
       <c r="L6" s="45"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="45"/>
       <c r="C7" s="45"/>
@@ -2817,7 +3589,7 @@
       <c r="K7" s="45"/>
       <c r="L7" s="45"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
@@ -2831,7 +3603,7 @@
       <c r="K8" s="45"/>
       <c r="L8" s="45"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
@@ -2845,7 +3617,7 @@
       <c r="K9" s="45"/>
       <c r="L9" s="45"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
@@ -2859,7 +3631,7 @@
       <c r="K10" s="45"/>
       <c r="L10" s="45"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="14"/>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
@@ -2873,7 +3645,7 @@
       <c r="K11" s="45"/>
       <c r="L11" s="45"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="14"/>
       <c r="B12" s="45"/>
       <c r="C12" s="45"/>
@@ -2887,7 +3659,7 @@
       <c r="K12" s="45"/>
       <c r="L12" s="45"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="45"/>
       <c r="C13" s="45"/>
@@ -2901,7 +3673,7 @@
       <c r="K13" s="45"/>
       <c r="L13" s="45"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="45"/>
       <c r="C14" s="45"/>
@@ -2915,7 +3687,7 @@
       <c r="K14" s="45"/>
       <c r="L14" s="45"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="45"/>
       <c r="C15" s="45"/>
@@ -2929,7 +3701,7 @@
       <c r="K15" s="45"/>
       <c r="L15" s="45"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="45"/>
       <c r="C16" s="45"/>
@@ -2943,7 +3715,7 @@
       <c r="K16" s="45"/>
       <c r="L16" s="45"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
@@ -2957,7 +3729,7 @@
       <c r="K17" s="45"/>
       <c r="L17" s="45"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
@@ -2971,7 +3743,7 @@
       <c r="K18" s="45"/>
       <c r="L18" s="45"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
@@ -2985,7 +3757,7 @@
       <c r="K19" s="45"/>
       <c r="L19" s="45"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
@@ -2999,7 +3771,7 @@
       <c r="K20" s="45"/>
       <c r="L20" s="45"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -3013,7 +3785,7 @@
       <c r="K21" s="45"/>
       <c r="L21" s="45"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="45"/>
       <c r="C22" s="45"/>
@@ -3027,7 +3799,7 @@
       <c r="K22" s="45"/>
       <c r="L22" s="45"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -3041,7 +3813,7 @@
       <c r="K23" s="45"/>
       <c r="L23" s="45"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="45"/>
       <c r="C24" s="45"/>
@@ -3055,7 +3827,7 @@
       <c r="K24" s="45"/>
       <c r="L24" s="45"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="45"/>
       <c r="C25" s="45"/>
@@ -3069,7 +3841,7 @@
       <c r="K25" s="45"/>
       <c r="L25" s="45"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="45"/>
       <c r="C26" s="45"/>
@@ -3083,7 +3855,7 @@
       <c r="K26" s="45"/>
       <c r="L26" s="45"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="45"/>
       <c r="C27" s="45"/>
@@ -3097,7 +3869,7 @@
       <c r="K27" s="45"/>
       <c r="L27" s="45"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="14"/>
       <c r="B28" s="45"/>
       <c r="C28" s="45"/>
@@ -3111,7 +3883,7 @@
       <c r="K28" s="45"/>
       <c r="L28" s="45"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="45"/>
       <c r="C29" s="45"/>
@@ -3125,7 +3897,7 @@
       <c r="K29" s="45"/>
       <c r="L29" s="45"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="45"/>
       <c r="C30" s="45"/>
@@ -3139,7 +3911,7 @@
       <c r="K30" s="45"/>
       <c r="L30" s="45"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="45"/>
       <c r="C31" s="45"/>
@@ -3153,7 +3925,7 @@
       <c r="K31" s="45"/>
       <c r="L31" s="45"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="45"/>
       <c r="C32" s="45"/>
@@ -3167,7 +3939,7 @@
       <c r="K32" s="45"/>
       <c r="L32" s="45"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="45"/>
       <c r="C33" s="45"/>
@@ -3181,7 +3953,7 @@
       <c r="K33" s="45"/>
       <c r="L33" s="45"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="14"/>
       <c r="B34" s="45"/>
       <c r="C34" s="45"/>
@@ -3195,7 +3967,7 @@
       <c r="K34" s="45"/>
       <c r="L34" s="45"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="14"/>
       <c r="B35" s="45"/>
       <c r="C35" s="45"/>
@@ -3209,7 +3981,7 @@
       <c r="K35" s="45"/>
       <c r="L35" s="45"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="14"/>
       <c r="B36" s="45"/>
       <c r="C36" s="45"/>
@@ -3223,7 +3995,7 @@
       <c r="K36" s="45"/>
       <c r="L36" s="45"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="14"/>
       <c r="B37" s="45"/>
       <c r="C37" s="45"/>
@@ -3237,7 +4009,7 @@
       <c r="K37" s="45"/>
       <c r="L37" s="45"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="14"/>
       <c r="B38" s="45"/>
       <c r="C38" s="45"/>
@@ -3251,7 +4023,7 @@
       <c r="K38" s="45"/>
       <c r="L38" s="45"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39" s="45"/>
       <c r="C39" s="45"/>
@@ -3265,7 +4037,7 @@
       <c r="K39" s="45"/>
       <c r="L39" s="45"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="14"/>
       <c r="B40" s="45"/>
       <c r="C40" s="45"/>
@@ -3279,7 +4051,7 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="14"/>
       <c r="B41" s="45"/>
       <c r="C41" s="45"/>
@@ -3293,7 +4065,7 @@
       <c r="K41" s="45"/>
       <c r="L41" s="45"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="14"/>
       <c r="B42" s="45"/>
       <c r="C42" s="45"/>
@@ -3307,7 +4079,7 @@
       <c r="K42" s="45"/>
       <c r="L42" s="45"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="14"/>
       <c r="B43" s="45"/>
       <c r="C43" s="45"/>
@@ -3321,7 +4093,7 @@
       <c r="K43" s="45"/>
       <c r="L43" s="45"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="14"/>
       <c r="B44" s="45"/>
       <c r="C44" s="45"/>
@@ -3335,7 +4107,7 @@
       <c r="K44" s="45"/>
       <c r="L44" s="45"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="14"/>
       <c r="B45" s="45"/>
       <c r="C45" s="45"/>
@@ -3349,7 +4121,7 @@
       <c r="K45" s="45"/>
       <c r="L45" s="45"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="14"/>
       <c r="B46" s="45"/>
       <c r="C46" s="45"/>
@@ -3363,7 +4135,7 @@
       <c r="K46" s="45"/>
       <c r="L46" s="45"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="14"/>
       <c r="B47" s="45"/>
       <c r="C47" s="45"/>
@@ -3377,7 +4149,7 @@
       <c r="K47" s="45"/>
       <c r="L47" s="45"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="14"/>
       <c r="B48" s="45"/>
       <c r="C48" s="45"/>
@@ -3391,7 +4163,7 @@
       <c r="K48" s="45"/>
       <c r="L48" s="45"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="14"/>
       <c r="B49" s="45"/>
       <c r="C49" s="45"/>
@@ -3405,7 +4177,7 @@
       <c r="K49" s="45"/>
       <c r="L49" s="45"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="14"/>
       <c r="B50" s="45"/>
       <c r="C50" s="45"/>
@@ -3419,7 +4191,7 @@
       <c r="K50" s="45"/>
       <c r="L50" s="45"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="14"/>
       <c r="B51" s="45"/>
       <c r="C51" s="45"/>
@@ -3433,7 +4205,7 @@
       <c r="K51" s="45"/>
       <c r="L51" s="45"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="14"/>
       <c r="B52" s="45"/>
       <c r="C52" s="45"/>
@@ -3447,7 +4219,7 @@
       <c r="K52" s="45"/>
       <c r="L52" s="45"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="14"/>
       <c r="B53" s="45"/>
       <c r="C53" s="45"/>
@@ -3461,7 +4233,7 @@
       <c r="K53" s="45"/>
       <c r="L53" s="45"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="14"/>
       <c r="B54" s="45"/>
       <c r="C54" s="45"/>
@@ -3475,7 +4247,7 @@
       <c r="K54" s="45"/>
       <c r="L54" s="45"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="14"/>
       <c r="B55" s="45"/>
       <c r="C55" s="45"/>
@@ -3489,7 +4261,7 @@
       <c r="K55" s="45"/>
       <c r="L55" s="45"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="14"/>
       <c r="B56" s="45"/>
       <c r="C56" s="45"/>
@@ -3503,7 +4275,7 @@
       <c r="K56" s="45"/>
       <c r="L56" s="45"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="14"/>
       <c r="B57" s="45"/>
       <c r="C57" s="45"/>
@@ -3517,7 +4289,7 @@
       <c r="K57" s="45"/>
       <c r="L57" s="45"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="14"/>
       <c r="B58" s="45"/>
       <c r="C58" s="45"/>
@@ -3531,7 +4303,7 @@
       <c r="K58" s="45"/>
       <c r="L58" s="45"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="14"/>
       <c r="B59" s="45"/>
       <c r="C59" s="45"/>
@@ -3545,7 +4317,7 @@
       <c r="K59" s="45"/>
       <c r="L59" s="45"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="14"/>
       <c r="B60" s="45"/>
       <c r="C60" s="45"/>
@@ -3559,7 +4331,7 @@
       <c r="K60" s="45"/>
       <c r="L60" s="45"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="14"/>
       <c r="B61" s="45"/>
       <c r="C61" s="45"/>
@@ -3573,7 +4345,7 @@
       <c r="K61" s="45"/>
       <c r="L61" s="45"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="14"/>
       <c r="B62" s="45"/>
       <c r="C62" s="45"/>
@@ -3587,7 +4359,7 @@
       <c r="K62" s="45"/>
       <c r="L62" s="45"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="14"/>
       <c r="B63" s="45"/>
       <c r="C63" s="45"/>
@@ -3601,7 +4373,7 @@
       <c r="K63" s="45"/>
       <c r="L63" s="45"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="14"/>
       <c r="B64" s="45"/>
       <c r="C64" s="45"/>
@@ -3615,7 +4387,7 @@
       <c r="K64" s="45"/>
       <c r="L64" s="45"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="14"/>
       <c r="B65" s="45"/>
       <c r="C65" s="45"/>
@@ -3629,7 +4401,7 @@
       <c r="K65" s="45"/>
       <c r="L65" s="45"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="14"/>
       <c r="B66" s="45"/>
       <c r="C66" s="45"/>
@@ -3643,7 +4415,7 @@
       <c r="K66" s="45"/>
       <c r="L66" s="45"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="14"/>
       <c r="B67" s="45"/>
       <c r="C67" s="45"/>
@@ -3657,7 +4429,7 @@
       <c r="K67" s="45"/>
       <c r="L67" s="45"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="14"/>
       <c r="B68" s="45"/>
       <c r="C68" s="45"/>
@@ -3671,7 +4443,7 @@
       <c r="K68" s="45"/>
       <c r="L68" s="45"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="14"/>
       <c r="B69" s="45"/>
       <c r="C69" s="45"/>
@@ -3685,7 +4457,7 @@
       <c r="K69" s="45"/>
       <c r="L69" s="45"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="14"/>
       <c r="B70" s="45"/>
       <c r="C70" s="45"/>
@@ -3699,7 +4471,7 @@
       <c r="K70" s="45"/>
       <c r="L70" s="45"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="14"/>
       <c r="B71" s="45"/>
       <c r="C71" s="45"/>
@@ -3713,7 +4485,7 @@
       <c r="K71" s="45"/>
       <c r="L71" s="45"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="14"/>
       <c r="B72" s="45"/>
       <c r="C72" s="45"/>
@@ -3733,25 +4505,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J60"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="6"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="22.7265625" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3783,7 +4555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -3815,7 +4587,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="16"/>
       <c r="C4" s="15"/>
@@ -3841,7 +4613,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14"/>
       <c r="B5" s="16"/>
       <c r="C5" s="15"/>
@@ -3867,7 +4639,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14"/>
       <c r="B6" s="16"/>
       <c r="C6" s="15"/>
@@ -3893,7 +4665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="16"/>
       <c r="C7" s="15"/>
@@ -3919,7 +4691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="16"/>
       <c r="C8" s="15"/>
@@ -3945,7 +4717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="16"/>
       <c r="C9" s="15"/>
@@ -3971,7 +4743,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10" s="15"/>
@@ -3997,7 +4769,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="14"/>
       <c r="B11" s="16"/>
       <c r="C11" s="15"/>
@@ -4023,7 +4795,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -4049,7 +4821,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13" s="15"/>
@@ -4075,7 +4847,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -4087,7 +4859,7 @@
       <c r="I14" s="17"/>
       <c r="J14" s="15"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -4099,7 +4871,7 @@
       <c r="I15" s="17"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>2</v>
       </c>
@@ -4131,7 +4903,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -4157,7 +4929,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -4183,7 +4955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -4209,7 +4981,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -4223,7 +4995,7 @@
       <c r="I20" s="17"/>
       <c r="J20" s="15"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -4237,7 +5009,7 @@
       <c r="I21" s="17"/>
       <c r="J21" s="15"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -4251,7 +5023,7 @@
       <c r="I22" s="17"/>
       <c r="J22" s="15"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -4265,7 +5037,7 @@
       <c r="I23" s="17"/>
       <c r="J23" s="15"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -4277,7 +5049,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="15"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -4289,7 +5061,7 @@
       <c r="I25" s="17"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>3</v>
       </c>
@@ -4319,7 +5091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
@@ -4331,7 +5103,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="15"/>
     </row>
-    <row r="28" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A28" s="14">
         <v>4</v>
       </c>
@@ -4363,7 +5135,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="16"/>
       <c r="C29" s="15"/>
@@ -4375,7 +5147,7 @@
       <c r="I29" s="14"/>
       <c r="J29" s="15"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="16"/>
       <c r="C30" s="15"/>
@@ -4387,7 +5159,7 @@
       <c r="I30" s="14"/>
       <c r="J30" s="15"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="16"/>
       <c r="C31" s="15"/>
@@ -4399,7 +5171,7 @@
       <c r="I31" s="14"/>
       <c r="J31" s="15"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="16"/>
       <c r="C32" s="15"/>
@@ -4411,7 +5183,7 @@
       <c r="I32" s="14"/>
       <c r="J32" s="15"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="16"/>
       <c r="C33" s="15"/>
@@ -4423,7 +5195,7 @@
       <c r="I33" s="14"/>
       <c r="J33" s="15"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="14"/>
       <c r="B34" s="16"/>
       <c r="C34" s="15"/>
@@ -4435,7 +5207,7 @@
       <c r="I34" s="14"/>
       <c r="J34" s="15"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="14"/>
       <c r="B35" s="16"/>
       <c r="C35" s="15"/>
@@ -4447,7 +5219,7 @@
       <c r="I35" s="14"/>
       <c r="J35" s="15"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="14"/>
       <c r="B36" s="16"/>
       <c r="C36" s="15"/>
@@ -4459,7 +5231,7 @@
       <c r="I36" s="14"/>
       <c r="J36" s="15"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="14"/>
       <c r="B37" s="16"/>
       <c r="C37" s="15"/>
@@ -4471,7 +5243,7 @@
       <c r="I37" s="14"/>
       <c r="J37" s="15"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="14"/>
       <c r="B38" s="16"/>
       <c r="C38" s="15"/>
@@ -4483,7 +5255,7 @@
       <c r="I38" s="14"/>
       <c r="J38" s="15"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="14"/>
       <c r="B39" s="16"/>
       <c r="C39" s="15"/>
@@ -4495,7 +5267,7 @@
       <c r="I39" s="14"/>
       <c r="J39" s="15"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="14"/>
       <c r="B40" s="16"/>
       <c r="C40" s="15"/>
@@ -4507,7 +5279,7 @@
       <c r="I40" s="14"/>
       <c r="J40" s="15"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="14"/>
       <c r="B41" s="16"/>
       <c r="C41" s="15"/>
@@ -4519,7 +5291,7 @@
       <c r="I41" s="14"/>
       <c r="J41" s="15"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="14"/>
       <c r="B42" s="16"/>
       <c r="C42" s="15"/>
@@ -4531,7 +5303,7 @@
       <c r="I42" s="14"/>
       <c r="J42" s="15"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="21"/>
       <c r="B43" s="23"/>
       <c r="C43" s="22"/>
@@ -4543,7 +5315,7 @@
       <c r="I43" s="21"/>
       <c r="J43" s="22"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="21"/>
       <c r="B44" s="23"/>
       <c r="C44" s="22"/>
@@ -4555,7 +5327,7 @@
       <c r="I44" s="21"/>
       <c r="J44" s="22"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="21"/>
       <c r="B45" s="23"/>
       <c r="C45" s="22"/>
@@ -4567,7 +5339,7 @@
       <c r="I45" s="21"/>
       <c r="J45" s="21"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="21"/>
       <c r="B46" s="23"/>
       <c r="C46" s="22"/>
@@ -4579,7 +5351,7 @@
       <c r="I46" s="21"/>
       <c r="J46" s="21"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="21"/>
       <c r="B47" s="23"/>
       <c r="C47" s="22"/>
@@ -4591,7 +5363,7 @@
       <c r="I47" s="21"/>
       <c r="J47" s="21"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="21"/>
       <c r="B48" s="23"/>
       <c r="C48" s="22"/>
@@ -4603,7 +5375,7 @@
       <c r="I48" s="21"/>
       <c r="J48" s="21"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="21"/>
       <c r="B49" s="23"/>
       <c r="C49" s="22"/>
@@ -4615,7 +5387,7 @@
       <c r="I49" s="21"/>
       <c r="J49" s="21"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="21"/>
       <c r="B50" s="23"/>
       <c r="C50" s="22"/>
@@ -4627,7 +5399,7 @@
       <c r="I50" s="21"/>
       <c r="J50" s="21"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="21"/>
       <c r="B51" s="23"/>
       <c r="C51" s="22"/>
@@ -4639,7 +5411,7 @@
       <c r="I51" s="21"/>
       <c r="J51" s="21"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="21"/>
       <c r="B52" s="23"/>
       <c r="C52" s="22"/>
@@ -4651,7 +5423,7 @@
       <c r="I52" s="21"/>
       <c r="J52" s="21"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="9"/>
       <c r="B53" s="26"/>
       <c r="C53" s="12"/>
@@ -4663,7 +5435,7 @@
       <c r="I53" s="9"/>
       <c r="J53" s="9"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="9"/>
       <c r="B54" s="26"/>
       <c r="C54" s="12"/>
@@ -4675,7 +5447,7 @@
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="9"/>
       <c r="B55" s="26"/>
       <c r="C55" s="12"/>
@@ -4687,7 +5459,7 @@
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="9"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12"/>
@@ -4699,7 +5471,7 @@
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="9"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12"/>
@@ -4711,7 +5483,7 @@
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="9"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12"/>
@@ -4723,7 +5495,7 @@
       <c r="I58" s="9"/>
       <c r="J58" s="9"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="9"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12"/>
@@ -4735,7 +5507,7 @@
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="9"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12"/>
@@ -4767,26 +5539,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF8A004-CF38-44BD-863F-49ADC296A5A4}">
   <dimension ref="A2:K45"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="31" customWidth="1"/>
-    <col min="12" max="16384" width="8.7109375" style="6"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1796875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" style="31" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4821,7 +5593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -4856,7 +5628,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="63" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -4891,7 +5663,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -4926,7 +5698,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -4959,7 +5731,7 @@
       </c>
       <c r="K6" s="20"/>
     </row>
-    <row r="7" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="93" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -4992,7 +5764,7 @@
       </c>
       <c r="K7" s="20"/>
     </row>
-    <row r="8" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -5025,7 +5797,7 @@
       </c>
       <c r="K8" s="20"/>
     </row>
-    <row r="9" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>7</v>
       </c>
@@ -5058,7 +5830,7 @@
       </c>
       <c r="K9" s="20"/>
     </row>
-    <row r="10" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>8</v>
       </c>
@@ -5091,7 +5863,7 @@
       </c>
       <c r="K10" s="20"/>
     </row>
-    <row r="11" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>9</v>
       </c>
@@ -5124,7 +5896,7 @@
       </c>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>10</v>
       </c>
@@ -5157,7 +5929,7 @@
       </c>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>11</v>
       </c>
@@ -5172,7 +5944,7 @@
       <c r="J13" s="27"/>
       <c r="K13" s="20"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -5185,7 +5957,7 @@
       <c r="J14" s="14"/>
       <c r="K14" s="20"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -5198,7 +5970,7 @@
       <c r="J15" s="14"/>
       <c r="K15" s="20"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="15"/>
@@ -5211,7 +5983,7 @@
       <c r="J16" s="14"/>
       <c r="K16" s="20"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -5224,7 +5996,7 @@
       <c r="J17" s="14"/>
       <c r="K17" s="20"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -5237,7 +6009,7 @@
       <c r="J18" s="14"/>
       <c r="K18" s="20"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -5250,7 +6022,7 @@
       <c r="J19" s="14"/>
       <c r="K19" s="20"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -5263,7 +6035,7 @@
       <c r="J20" s="14"/>
       <c r="K20" s="20"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -5276,7 +6048,7 @@
       <c r="J21" s="14"/>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -5289,7 +6061,7 @@
       <c r="J22" s="14"/>
       <c r="K22" s="20"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -5302,7 +6074,7 @@
       <c r="J23" s="14"/>
       <c r="K23" s="20"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -5315,7 +6087,7 @@
       <c r="J24" s="14"/>
       <c r="K24" s="20"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -5328,7 +6100,7 @@
       <c r="J25" s="14"/>
       <c r="K25" s="20"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -5341,7 +6113,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="20"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
@@ -5354,7 +6126,7 @@
       <c r="J27" s="14"/>
       <c r="K27" s="20"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
       <c r="B28" s="23"/>
       <c r="C28" s="22"/>
@@ -5367,7 +6139,7 @@
       <c r="J28" s="21"/>
       <c r="K28" s="25"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="23"/>
       <c r="C29" s="22"/>
@@ -5380,7 +6152,7 @@
       <c r="J29" s="21"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
       <c r="B30" s="23"/>
       <c r="C30" s="22"/>
@@ -5393,7 +6165,7 @@
       <c r="J30" s="21"/>
       <c r="K30" s="29"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="23"/>
       <c r="C31" s="22"/>
@@ -5406,7 +6178,7 @@
       <c r="J31" s="21"/>
       <c r="K31" s="29"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
       <c r="B32" s="23"/>
       <c r="C32" s="22"/>
@@ -5419,7 +6191,7 @@
       <c r="J32" s="21"/>
       <c r="K32" s="29"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="23"/>
       <c r="C33" s="22"/>
@@ -5432,7 +6204,7 @@
       <c r="J33" s="21"/>
       <c r="K33" s="29"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="23"/>
       <c r="C34" s="22"/>
@@ -5445,7 +6217,7 @@
       <c r="J34" s="21"/>
       <c r="K34" s="29"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="23"/>
       <c r="C35" s="22"/>
@@ -5458,7 +6230,7 @@
       <c r="J35" s="21"/>
       <c r="K35" s="29"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
       <c r="B36" s="23"/>
       <c r="C36" s="22"/>
@@ -5471,7 +6243,7 @@
       <c r="J36" s="21"/>
       <c r="K36" s="29"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="23"/>
       <c r="C37" s="22"/>
@@ -5484,7 +6256,7 @@
       <c r="J37" s="21"/>
       <c r="K37" s="29"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="26"/>
       <c r="C38" s="12"/>
@@ -5497,7 +6269,7 @@
       <c r="J38" s="9"/>
       <c r="K38" s="30"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="26"/>
       <c r="C39" s="12"/>
@@ -5510,7 +6282,7 @@
       <c r="J39" s="9"/>
       <c r="K39" s="30"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="26"/>
       <c r="C40" s="12"/>
@@ -5523,7 +6295,7 @@
       <c r="J40" s="9"/>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -5536,7 +6308,7 @@
       <c r="J41" s="9"/>
       <c r="K41" s="30"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -5549,7 +6321,7 @@
       <c r="J42" s="9"/>
       <c r="K42" s="30"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -5562,7 +6334,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="30"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -5575,7 +6347,7 @@
       <c r="J44" s="9"/>
       <c r="K44" s="30"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="9"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -5608,24 +6380,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F27FD917-4FA6-4015-8A7A-FAFD0337D20E}">
   <dimension ref="A2:I45"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="31" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="6"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="31" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -5654,7 +6426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -5681,7 +6453,7 @@
       </c>
       <c r="I3" s="20"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -5694,7 +6466,7 @@
       <c r="H4" s="27"/>
       <c r="I4" s="20"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -5707,7 +6479,7 @@
       <c r="H5" s="27"/>
       <c r="I5" s="20"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -5720,7 +6492,7 @@
       <c r="H6" s="27"/>
       <c r="I6" s="20"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -5733,7 +6505,7 @@
       <c r="H7" s="27"/>
       <c r="I7" s="20"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -5746,7 +6518,7 @@
       <c r="H8" s="27"/>
       <c r="I8" s="20"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>7</v>
       </c>
@@ -5759,7 +6531,7 @@
       <c r="H9" s="27"/>
       <c r="I9" s="20"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>8</v>
       </c>
@@ -5772,7 +6544,7 @@
       <c r="H10" s="27"/>
       <c r="I10" s="20"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>9</v>
       </c>
@@ -5785,7 +6557,7 @@
       <c r="H11" s="27"/>
       <c r="I11" s="20"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>10</v>
       </c>
@@ -5798,7 +6570,7 @@
       <c r="H12" s="27"/>
       <c r="I12" s="20"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>11</v>
       </c>
@@ -5811,7 +6583,7 @@
       <c r="H13" s="27"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -5822,7 +6594,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="20"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -5833,7 +6605,7 @@
       <c r="H15" s="14"/>
       <c r="I15" s="20"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="15"/>
@@ -5844,7 +6616,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -5855,7 +6627,7 @@
       <c r="H17" s="14"/>
       <c r="I17" s="20"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -5866,7 +6638,7 @@
       <c r="H18" s="14"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -5877,7 +6649,7 @@
       <c r="H19" s="14"/>
       <c r="I19" s="20"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -5888,7 +6660,7 @@
       <c r="H20" s="14"/>
       <c r="I20" s="20"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -5899,7 +6671,7 @@
       <c r="H21" s="14"/>
       <c r="I21" s="20"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -5910,7 +6682,7 @@
       <c r="H22" s="14"/>
       <c r="I22" s="20"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -5921,7 +6693,7 @@
       <c r="H23" s="14"/>
       <c r="I23" s="20"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -5932,7 +6704,7 @@
       <c r="H24" s="14"/>
       <c r="I24" s="20"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -5943,7 +6715,7 @@
       <c r="H25" s="14"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -5954,7 +6726,7 @@
       <c r="H26" s="14"/>
       <c r="I26" s="20"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
@@ -5965,7 +6737,7 @@
       <c r="H27" s="14"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
       <c r="B28" s="23"/>
       <c r="C28" s="22"/>
@@ -5976,7 +6748,7 @@
       <c r="H28" s="21"/>
       <c r="I28" s="25"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="23"/>
       <c r="C29" s="22"/>
@@ -5987,7 +6759,7 @@
       <c r="H29" s="21"/>
       <c r="I29" s="25"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
       <c r="B30" s="23"/>
       <c r="C30" s="22"/>
@@ -5998,7 +6770,7 @@
       <c r="H30" s="21"/>
       <c r="I30" s="29"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="23"/>
       <c r="C31" s="22"/>
@@ -6009,7 +6781,7 @@
       <c r="H31" s="21"/>
       <c r="I31" s="29"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
       <c r="B32" s="23"/>
       <c r="C32" s="22"/>
@@ -6020,7 +6792,7 @@
       <c r="H32" s="21"/>
       <c r="I32" s="29"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="23"/>
       <c r="C33" s="22"/>
@@ -6031,7 +6803,7 @@
       <c r="H33" s="21"/>
       <c r="I33" s="29"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="23"/>
       <c r="C34" s="22"/>
@@ -6042,7 +6814,7 @@
       <c r="H34" s="21"/>
       <c r="I34" s="29"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="23"/>
       <c r="C35" s="22"/>
@@ -6053,7 +6825,7 @@
       <c r="H35" s="21"/>
       <c r="I35" s="29"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
       <c r="B36" s="23"/>
       <c r="C36" s="22"/>
@@ -6064,7 +6836,7 @@
       <c r="H36" s="21"/>
       <c r="I36" s="29"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="23"/>
       <c r="C37" s="22"/>
@@ -6075,7 +6847,7 @@
       <c r="H37" s="21"/>
       <c r="I37" s="29"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="26"/>
       <c r="C38" s="12"/>
@@ -6086,7 +6858,7 @@
       <c r="H38" s="9"/>
       <c r="I38" s="30"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="26"/>
       <c r="C39" s="12"/>
@@ -6097,7 +6869,7 @@
       <c r="H39" s="9"/>
       <c r="I39" s="30"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="26"/>
       <c r="C40" s="12"/>
@@ -6108,7 +6880,7 @@
       <c r="H40" s="9"/>
       <c r="I40" s="30"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -6119,7 +6891,7 @@
       <c r="H41" s="9"/>
       <c r="I41" s="30"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -6130,7 +6902,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="30"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -6141,7 +6913,7 @@
       <c r="H43" s="9"/>
       <c r="I43" s="30"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -6152,7 +6924,7 @@
       <c r="H44" s="9"/>
       <c r="I44" s="30"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="9"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -6169,25 +6941,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE6CA21-7FAF-4F55-9AE9-BF67A11BF232}">
   <dimension ref="A2:J45"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="25.7265625" style="13" customWidth="1"/>
     <col min="5" max="5" width="50" style="8" customWidth="1"/>
-    <col min="6" max="6" width="41.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="31" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="6"/>
+    <col min="6" max="6" width="41.81640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="18.7265625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" style="31" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
         <v>242</v>
       </c>
@@ -6219,11 +6991,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="51">
+    <row r="3" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>225</v>
       </c>
       <c r="C3" s="16" t="s">
@@ -6232,44 +7004,44 @@
       <c r="D3" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="53" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="49">
+      <c r="G3" s="50">
         <v>48</v>
       </c>
-      <c r="H3" s="49" t="s">
+      <c r="H3" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="J3" s="49"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="50"/>
+      <c r="J3" s="50"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="58"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="43" t="s">
         <v>230</v>
       </c>
       <c r="D4" s="42" t="s">
         <v>231</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="50"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="51">
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="56">
         <v>2</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="50" t="s">
         <v>238</v>
       </c>
       <c r="C5" s="43" t="s">
@@ -6278,76 +7050,76 @@
       <c r="D5" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="53" t="s">
         <v>237</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="50">
         <v>24</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="47">
         <v>45967</v>
       </c>
-      <c r="I5" s="55" t="s">
+      <c r="I5" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="J5" s="49"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="54"/>
+      <c r="J5" s="50"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="57"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="16" t="s">
         <v>232</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="54"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="51"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="57"/>
+      <c r="B7" s="51"/>
       <c r="C7" s="16" t="s">
         <v>233</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="54"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="50"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="51"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="58"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="16" t="s">
         <v>234</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="50"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="51">
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="52"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="56">
         <v>3</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="50" t="s">
         <v>273</v>
       </c>
       <c r="C9" s="43" t="s">
@@ -6356,88 +7128,88 @@
       <c r="D9" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="F9" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="50">
         <v>12</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="47">
         <v>46157</v>
       </c>
-      <c r="I9" s="55" t="s">
+      <c r="I9" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="J9" s="49"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="54"/>
+      <c r="J9" s="50"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="57"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="16" t="s">
         <v>274</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="54"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="54"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="51"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="57"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="16" t="s">
         <v>275</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="54"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="54"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="51"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="57"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="16" t="s">
         <v>276</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="54"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="53"/>
-      <c r="B13" s="50"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="51"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="58"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="16" t="s">
         <v>277</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="52"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -6449,7 +7221,7 @@
       <c r="I14" s="14"/>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -6461,7 +7233,7 @@
       <c r="I15" s="14"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="15"/>
@@ -6473,7 +7245,7 @@
       <c r="I16" s="14"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -6485,7 +7257,7 @@
       <c r="I17" s="14"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -6497,7 +7269,7 @@
       <c r="I18" s="14"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -6509,7 +7281,7 @@
       <c r="I19" s="14"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -6521,7 +7293,7 @@
       <c r="I20" s="14"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -6533,7 +7305,7 @@
       <c r="I21" s="14"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -6545,7 +7317,7 @@
       <c r="I22" s="14"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -6557,7 +7329,7 @@
       <c r="I23" s="14"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -6569,7 +7341,7 @@
       <c r="I24" s="14"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -6581,7 +7353,7 @@
       <c r="I25" s="14"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -6593,7 +7365,7 @@
       <c r="I26" s="14"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
@@ -6605,7 +7377,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
       <c r="B28" s="23"/>
       <c r="C28" s="22"/>
@@ -6617,7 +7389,7 @@
       <c r="I28" s="21"/>
       <c r="J28" s="25"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="23"/>
       <c r="C29" s="22"/>
@@ -6629,7 +7401,7 @@
       <c r="I29" s="21"/>
       <c r="J29" s="25"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
       <c r="B30" s="23"/>
       <c r="C30" s="22"/>
@@ -6641,7 +7413,7 @@
       <c r="I30" s="21"/>
       <c r="J30" s="29"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="23"/>
       <c r="C31" s="22"/>
@@ -6653,7 +7425,7 @@
       <c r="I31" s="21"/>
       <c r="J31" s="29"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
       <c r="B32" s="23"/>
       <c r="C32" s="22"/>
@@ -6665,7 +7437,7 @@
       <c r="I32" s="21"/>
       <c r="J32" s="29"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="23"/>
       <c r="C33" s="22"/>
@@ -6677,7 +7449,7 @@
       <c r="I33" s="21"/>
       <c r="J33" s="29"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="23"/>
       <c r="C34" s="22"/>
@@ -6689,7 +7461,7 @@
       <c r="I34" s="21"/>
       <c r="J34" s="29"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="23"/>
       <c r="C35" s="22"/>
@@ -6701,7 +7473,7 @@
       <c r="I35" s="21"/>
       <c r="J35" s="29"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
       <c r="B36" s="23"/>
       <c r="C36" s="22"/>
@@ -6713,7 +7485,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="29"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="21"/>
       <c r="B37" s="23"/>
       <c r="C37" s="22"/>
@@ -6725,7 +7497,7 @@
       <c r="I37" s="21"/>
       <c r="J37" s="29"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="26"/>
       <c r="C38" s="12"/>
@@ -6737,7 +7509,7 @@
       <c r="I38" s="9"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="26"/>
       <c r="C39" s="12"/>
@@ -6749,7 +7521,7 @@
       <c r="I39" s="9"/>
       <c r="J39" s="30"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="26"/>
       <c r="C40" s="12"/>
@@ -6761,7 +7533,7 @@
       <c r="I40" s="9"/>
       <c r="J40" s="30"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -6773,7 +7545,7 @@
       <c r="I41" s="9"/>
       <c r="J41" s="30"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -6785,7 +7557,7 @@
       <c r="I42" s="9"/>
       <c r="J42" s="30"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -6797,7 +7569,7 @@
       <c r="I43" s="9"/>
       <c r="J43" s="30"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -6809,7 +7581,7 @@
       <c r="I44" s="9"/>
       <c r="J44" s="30"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="9"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12"/>
@@ -6823,6 +7595,21 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="F9:F13"/>
+    <mergeCell ref="G9:G13"/>
+    <mergeCell ref="H9:H13"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
     <mergeCell ref="I9:I13"/>
     <mergeCell ref="J9:J13"/>
     <mergeCell ref="E9:E13"/>
@@ -6830,47 +7617,32 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="E5:E8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
     <mergeCell ref="J5:J8"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="F9:F13"/>
-    <mergeCell ref="G9:G13"/>
-    <mergeCell ref="H9:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41BD6938-CF4E-43E9-92B7-2BAB94E3A4C1}">
   <dimension ref="A2:I44"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" style="8" customWidth="1"/>
     <col min="3" max="3" width="24" style="13" customWidth="1"/>
     <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="6"/>
+    <col min="5" max="5" width="41.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.1796875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="18.1796875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7265625" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -6899,7 +7671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -6926,7 +7698,7 @@
       </c>
       <c r="I3" s="15"/>
     </row>
-    <row r="4" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -6953,7 +7725,7 @@
       </c>
       <c r="I4" s="15"/>
     </row>
-    <row r="5" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>3</v>
       </c>
@@ -6980,7 +7752,7 @@
       </c>
       <c r="I5" s="15"/>
     </row>
-    <row r="6" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>4</v>
       </c>
@@ -7007,7 +7779,7 @@
       </c>
       <c r="I6" s="15"/>
     </row>
-    <row r="7" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>5</v>
       </c>
@@ -7034,7 +7806,7 @@
       </c>
       <c r="I7" s="15"/>
     </row>
-    <row r="8" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>6</v>
       </c>
@@ -7061,7 +7833,7 @@
       </c>
       <c r="I8" s="15"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="16"/>
       <c r="C9" s="15"/>
@@ -7072,7 +7844,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="15"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="16"/>
       <c r="C10" s="15"/>
@@ -7083,7 +7855,7 @@
       <c r="H10" s="17"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="14"/>
       <c r="B11" s="16"/>
       <c r="C11" s="15"/>
@@ -7094,7 +7866,7 @@
       <c r="H11" s="14"/>
       <c r="I11" s="15"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="14"/>
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
@@ -7105,7 +7877,7 @@
       <c r="H12" s="14"/>
       <c r="I12" s="15"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="14"/>
       <c r="B13" s="16"/>
       <c r="C13" s="15"/>
@@ -7116,7 +7888,7 @@
       <c r="H13" s="14"/>
       <c r="I13" s="15"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="16"/>
       <c r="C14" s="15"/>
@@ -7127,7 +7899,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="15"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="16"/>
       <c r="C15" s="15"/>
@@ -7138,7 +7910,7 @@
       <c r="H15" s="14"/>
       <c r="I15" s="15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="16"/>
       <c r="C16" s="15"/>
@@ -7149,7 +7921,7 @@
       <c r="H16" s="14"/>
       <c r="I16" s="15"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="16"/>
       <c r="C17" s="15"/>
@@ -7160,7 +7932,7 @@
       <c r="H17" s="14"/>
       <c r="I17" s="15"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="14"/>
       <c r="B18" s="16"/>
       <c r="C18" s="15"/>
@@ -7171,7 +7943,7 @@
       <c r="H18" s="14"/>
       <c r="I18" s="15"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
@@ -7182,7 +7954,7 @@
       <c r="H19" s="14"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="16"/>
       <c r="C20" s="15"/>
@@ -7193,7 +7965,7 @@
       <c r="H20" s="14"/>
       <c r="I20" s="15"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="16"/>
       <c r="C21" s="15"/>
@@ -7204,7 +7976,7 @@
       <c r="H21" s="14"/>
       <c r="I21" s="15"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="16"/>
       <c r="C22" s="15"/>
@@ -7215,7 +7987,7 @@
       <c r="H22" s="14"/>
       <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="16"/>
       <c r="C23" s="15"/>
@@ -7226,7 +7998,7 @@
       <c r="H23" s="14"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24" s="16"/>
       <c r="C24" s="15"/>
@@ -7237,7 +8009,7 @@
       <c r="H24" s="14"/>
       <c r="I24" s="15"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25" s="16"/>
       <c r="C25" s="15"/>
@@ -7248,7 +8020,7 @@
       <c r="H25" s="14"/>
       <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
@@ -7259,7 +8031,7 @@
       <c r="H26" s="14"/>
       <c r="I26" s="15"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="21"/>
       <c r="B27" s="23"/>
       <c r="C27" s="22"/>
@@ -7270,7 +8042,7 @@
       <c r="H27" s="21"/>
       <c r="I27" s="22"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="21"/>
       <c r="B28" s="23"/>
       <c r="C28" s="22"/>
@@ -7281,7 +8053,7 @@
       <c r="H28" s="21"/>
       <c r="I28" s="22"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="21"/>
       <c r="B29" s="23"/>
       <c r="C29" s="22"/>
@@ -7292,7 +8064,7 @@
       <c r="H29" s="21"/>
       <c r="I29" s="21"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="21"/>
       <c r="B30" s="23"/>
       <c r="C30" s="22"/>
@@ -7303,7 +8075,7 @@
       <c r="H30" s="21"/>
       <c r="I30" s="21"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="21"/>
       <c r="B31" s="23"/>
       <c r="C31" s="22"/>
@@ -7314,7 +8086,7 @@
       <c r="H31" s="21"/>
       <c r="I31" s="21"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="21"/>
       <c r="B32" s="23"/>
       <c r="C32" s="22"/>
@@ -7325,7 +8097,7 @@
       <c r="H32" s="21"/>
       <c r="I32" s="21"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="21"/>
       <c r="B33" s="23"/>
       <c r="C33" s="22"/>
@@ -7336,7 +8108,7 @@
       <c r="H33" s="21"/>
       <c r="I33" s="21"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="23"/>
       <c r="C34" s="22"/>
@@ -7347,7 +8119,7 @@
       <c r="H34" s="21"/>
       <c r="I34" s="21"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="21"/>
       <c r="B35" s="23"/>
       <c r="C35" s="22"/>
@@ -7358,7 +8130,7 @@
       <c r="H35" s="21"/>
       <c r="I35" s="21"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="21"/>
       <c r="B36" s="23"/>
       <c r="C36" s="22"/>
@@ -7369,7 +8141,7 @@
       <c r="H36" s="21"/>
       <c r="I36" s="21"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="26"/>
       <c r="C37" s="12"/>
@@ -7380,7 +8152,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="26"/>
       <c r="C38" s="12"/>
@@ -7391,7 +8163,7 @@
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="26"/>
       <c r="C39" s="12"/>
@@ -7402,7 +8174,7 @@
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12"/>
@@ -7413,7 +8185,7 @@
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12"/>
@@ -7424,7 +8196,7 @@
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12"/>
@@ -7435,7 +8207,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
@@ -7446,7 +8218,7 @@
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="9"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12"/>
@@ -7469,607 +8241,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{329D78CB-96B5-4BE9-A9C4-C501614BBAAD}">
-  <dimension ref="A2:J44"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="24" style="13" customWidth="1"/>
-    <col min="4" max="4" width="50" style="8" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="15"/>
-    </row>
-    <row r="4" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
-        <v>2</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="15"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
-        <v>3</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="15"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>4</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="15"/>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="22"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="22"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="21"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="21"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="J3:J36">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"Accept"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"Under Review"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"Reject"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Work_Track.xlsx
+++ b/Work_Track.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dinesh_Academic\Projects\VS_Projects\ProfApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A8FE3F-5096-4670-8B70-A3ECEDF42D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607F2A01-FA41-495D-8A00-122EB9CDC28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="602" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="602" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Academic" sheetId="2" r:id="rId1"/>
@@ -24,18 +24,31 @@
     <sheet name="Conferences" sheetId="4" r:id="rId9"/>
     <sheet name="Ideas" sheetId="5" r:id="rId10"/>
     <sheet name="History_record" sheetId="6" r:id="rId11"/>
+    <sheet name="Users" sheetId="14" r:id="rId12"/>
+    <sheet name="Contact" sheetId="16" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="314">
   <si>
     <t>S. No.</t>
   </si>
@@ -547,9 +560,6 @@
     <t>Educational Details</t>
   </si>
   <si>
-    <t>Post-PhD</t>
-  </si>
-  <si>
     <t>Class X (AISSE)</t>
   </si>
   <si>
@@ -817,9 +827,6 @@
     <t>Sole Supervisor</t>
   </si>
   <si>
-    <t>Joint Supervsor</t>
-  </si>
-  <si>
     <t>Ramya Madhavaram</t>
   </si>
   <si>
@@ -890,13 +897,106 @@
   </si>
   <si>
     <t>Work Exp</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>kdinesh</t>
+  </si>
+  <si>
+    <t>Kd94@profweb</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>K Dinesh</t>
+  </si>
+  <si>
+    <t>Prof. K Dinesh</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>profkdinesh@gmail.com</t>
+  </si>
+  <si>
+    <t>kdinesh@nitw.ac.in</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>91-870-2465038</t>
+  </si>
+  <si>
+    <t>Address Line 1</t>
+  </si>
+  <si>
+    <t>Address Line 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS204, Department of Management Studies, </t>
+  </si>
+  <si>
+    <t>National Institute of Technology Warangal, Hanamkonda</t>
+  </si>
+  <si>
+    <t>Address Line 3</t>
+  </si>
+  <si>
+    <t>Telangana 506004, India</t>
+  </si>
+  <si>
+    <t>ORCID</t>
+  </si>
+  <si>
+    <t>Researchgate</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>Scholar</t>
+  </si>
+  <si>
+    <t>https://scholar.google.com/citations?user=B9iz-gQAAAAJ&amp;hl=en&amp;oi=ao</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/authid/detail.uri?authorId=57210416499</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kkdinesh/</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/profile/Kamala-Kannan-Dinesh</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-8956-8465</t>
+  </si>
+  <si>
+    <t>Joint Supervisor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,6 +1024,28 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1022,10 +1144,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1197,8 +1320,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
@@ -1590,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8EC06E-E612-4927-AA85-EB849A64B331}">
-  <dimension ref="B4:G19"/>
+  <dimension ref="B4:G11"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="34"/>
@@ -1613,19 +1743,19 @@
         <v>0</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -1633,10 +1763,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E6" s="38"/>
       <c r="F6" s="38">
@@ -1651,10 +1781,10 @@
         <v>2</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="38">
@@ -1669,10 +1799,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E8" s="38">
         <v>40784</v>
@@ -1689,10 +1819,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E9" s="38">
         <v>42214</v>
@@ -1709,10 +1839,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E10" s="38">
         <v>43101</v>
@@ -1728,152 +1858,6 @@
       <c r="B11" s="35"/>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="C12" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="33"/>
-    </row>
-    <row r="13" spans="2:7" s="36" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B14" s="14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" s="38">
-        <v>44216</v>
-      </c>
-      <c r="F14" s="38">
-        <v>44742</v>
-      </c>
-      <c r="G14" s="46">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B15" s="14">
-        <v>2</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" s="38">
-        <v>44743</v>
-      </c>
-      <c r="F15" s="38">
-        <v>44926</v>
-      </c>
-      <c r="G15" s="46">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B16" s="14">
-        <v>3</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E16" s="38">
-        <v>45057</v>
-      </c>
-      <c r="F16" s="38">
-        <v>45169</v>
-      </c>
-      <c r="G16" s="46">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" s="14">
-        <v>4</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="38">
-        <v>45200</v>
-      </c>
-      <c r="F17" s="38">
-        <v>45291</v>
-      </c>
-      <c r="G17" s="46">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B18" s="14">
-        <v>5</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="E18" s="38">
-        <v>45306</v>
-      </c>
-      <c r="F18" s="38">
-        <v>45869</v>
-      </c>
-      <c r="G18" s="46">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B19" s="14">
-        <v>6</v>
-      </c>
-      <c r="C19" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="E19" s="38">
-        <v>45880</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="G19" s="14">
-        <v>111188</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3180,6 +3164,183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8579A3B9-8840-4D67-962F-C12796B92DAF}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{9470CB24-902A-4DBE-8B51-E9B1D5226B81}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D8F7EA8-A9B3-473F-9D94-C86B5032E46B}">
+  <dimension ref="A2:C13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.1796875" style="61" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="61" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="61" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="61" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="61" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="61" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="61" t="s">
+        <v>305</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="61" t="s">
+        <v>306</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="61" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{10DFF167-F68C-4831-879F-2817F10C46FE}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{F8268063-69CD-4631-B928-A6F6A3600B9F}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{308E875D-E083-4C7F-8E8E-0DF25269D594}"/>
+    <hyperlink ref="B13" r:id="rId4" xr:uid="{0CAA5FE7-1CA4-4AFA-8E29-1D6515FEFE9B}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{5A5E9386-0859-4D0B-88DA-A9B48EA02D91}"/>
+    <hyperlink ref="B10" r:id="rId6" xr:uid="{40FDD64F-7811-453B-BC7A-CBCE093E8AD2}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{11A2C580-3E56-4CCD-B81C-8F282A48961B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0D01FD-168F-4E05-9976-928259C73ACA}">
   <dimension ref="B4:G11"/>
@@ -3196,7 +3357,7 @@
   <sheetData>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C4" s="33" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D4" s="33"/>
     </row>
@@ -3208,13 +3369,13 @@
         <v>167</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>7</v>
@@ -3225,10 +3386,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E6" s="38">
         <v>44216</v>
@@ -3248,7 +3409,7 @@
         <v>168</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E7" s="38">
         <v>44743</v>
@@ -3265,10 +3426,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E8" s="38">
         <v>45057</v>
@@ -3285,10 +3446,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E9" s="38">
         <v>45200</v>
@@ -3305,10 +3466,10 @@
         <v>5</v>
       </c>
       <c r="C10" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>185</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>186</v>
       </c>
       <c r="E10" s="38">
         <v>45306</v>
@@ -3325,16 +3486,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>188</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>189</v>
       </c>
       <c r="E11" s="38">
         <v>45880</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G11" s="14">
         <v>111188</v>
@@ -3359,7 +3520,7 @@
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B2" s="36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="36" customFormat="1" x14ac:dyDescent="0.35">
@@ -3367,16 +3528,16 @@
         <v>0</v>
       </c>
       <c r="B3" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3384,60 +3545,68 @@
         <v>1</v>
       </c>
       <c r="B4" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>197</v>
       </c>
       <c r="D4" s="17">
         <v>45883</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>2</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="17">
         <v>45883</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D6" s="17">
         <v>45883</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>4</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" s="17">
         <v>45883</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="59">
+        <v>46204</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
@@ -3482,34 +3651,34 @@
         <v>0</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>7</v>
@@ -3520,15 +3689,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C4" s="45"/>
       <c r="D4" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E4" s="45"/>
       <c r="F4" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="45"/>
@@ -3542,18 +3711,18 @@
         <v>2</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E5" s="45"/>
       <c r="F5" s="14" t="s">
-        <v>260</v>
+        <v>313</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H5" s="45"/>
       <c r="I5" s="45"/>
@@ -4592,13 +4761,13 @@
       <c r="B4" s="16"/>
       <c r="C4" s="15"/>
       <c r="D4" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="16" t="s">
         <v>202</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>203</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>10</v>
@@ -4754,7 +4923,7 @@
         <v>67</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>10</v>
@@ -4777,10 +4946,10 @@
         <v>8</v>
       </c>
       <c r="E11" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F11" s="16" t="s">
         <v>213</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>214</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>54</v>
@@ -4800,13 +4969,13 @@
       <c r="B12" s="16"/>
       <c r="C12" s="15"/>
       <c r="D12" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>245</v>
-      </c>
       <c r="F12" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>10</v>
@@ -4826,13 +4995,13 @@
       <c r="B13" s="16"/>
       <c r="C13" s="15"/>
       <c r="D13" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>18</v>
@@ -4844,7 +5013,7 @@
         <v>46059</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -4940,7 +5109,7 @@
         <v>149</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>10</v>
@@ -4960,13 +5129,13 @@
       <c r="B19" s="16"/>
       <c r="C19" s="15"/>
       <c r="D19" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="F19" s="16" t="s">
         <v>216</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>217</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>10</v>
@@ -4978,7 +5147,7 @@
         <v>45989</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -5108,19 +5277,19 @@
         <v>4</v>
       </c>
       <c r="B28" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>210</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>211</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>18</v>
@@ -5132,7 +5301,7 @@
         <v>45960</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
@@ -5587,7 +5756,7 @@
         <v>34</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K2" s="28" t="s">
         <v>7</v>
@@ -5616,7 +5785,7 @@
         <v>36</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I3" s="27" t="s">
         <v>144</v>
@@ -5625,7 +5794,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="62" x14ac:dyDescent="0.35">
@@ -5651,16 +5820,16 @@
         <v>36</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I4" s="27" t="s">
         <v>40</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
@@ -5692,10 +5861,10 @@
         <v>46</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="77.5" x14ac:dyDescent="0.35">
@@ -5727,7 +5896,7 @@
         <v>53</v>
       </c>
       <c r="J6" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K6" s="20"/>
     </row>
@@ -5760,7 +5929,7 @@
         <v>51</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K7" s="20"/>
     </row>
@@ -5793,7 +5962,7 @@
         <v>66</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K8" s="20"/>
     </row>
@@ -5826,7 +5995,7 @@
         <v>71</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K9" s="20"/>
     </row>
@@ -5859,7 +6028,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K10" s="20"/>
     </row>
@@ -5892,7 +6061,7 @@
         <v>81</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K11" s="20"/>
     </row>
@@ -5925,7 +6094,7 @@
         <v>86</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K12" s="20"/>
     </row>
@@ -6961,31 +7130,31 @@
   <sheetData>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="J2" s="28" t="s">
         <v>7</v>
@@ -6996,19 +7165,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="53" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G3" s="50">
         <v>48</v>
@@ -7017,7 +7186,7 @@
         <v>54</v>
       </c>
       <c r="I3" s="47" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J3" s="50"/>
     </row>
@@ -7025,10 +7194,10 @@
       <c r="A4" s="58"/>
       <c r="B4" s="52"/>
       <c r="C4" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>230</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>231</v>
       </c>
       <c r="E4" s="55"/>
       <c r="F4" s="55"/>
@@ -7042,19 +7211,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F5" s="53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G5" s="50">
         <v>24</v>
@@ -7063,7 +7232,7 @@
         <v>45967</v>
       </c>
       <c r="I5" s="47" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J5" s="50"/>
     </row>
@@ -7071,10 +7240,10 @@
       <c r="A6" s="57"/>
       <c r="B6" s="51"/>
       <c r="C6" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E6" s="54"/>
       <c r="F6" s="54"/>
@@ -7087,10 +7256,10 @@
       <c r="A7" s="57"/>
       <c r="B7" s="51"/>
       <c r="C7" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E7" s="54"/>
       <c r="F7" s="54"/>
@@ -7103,10 +7272,10 @@
       <c r="A8" s="58"/>
       <c r="B8" s="52"/>
       <c r="C8" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="55"/>
@@ -7120,19 +7289,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D9" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E9" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="50" t="s">
-        <v>280</v>
-      </c>
       <c r="F9" s="50" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G9" s="50">
         <v>12</v>
@@ -7141,7 +7310,7 @@
         <v>46157</v>
       </c>
       <c r="I9" s="47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J9" s="50"/>
     </row>
@@ -7149,10 +7318,10 @@
       <c r="A10" s="57"/>
       <c r="B10" s="51"/>
       <c r="C10" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E10" s="51"/>
       <c r="F10" s="51"/>
@@ -7165,10 +7334,10 @@
       <c r="A11" s="57"/>
       <c r="B11" s="51"/>
       <c r="C11" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E11" s="51"/>
       <c r="F11" s="51"/>
@@ -7181,10 +7350,10 @@
       <c r="A12" s="57"/>
       <c r="B12" s="51"/>
       <c r="C12" s="16" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
@@ -7197,10 +7366,10 @@
       <c r="A13" s="58"/>
       <c r="B13" s="52"/>
       <c r="C13" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>277</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>279</v>
       </c>
       <c r="E13" s="52"/>
       <c r="F13" s="52"/>
